--- a/Task Report/Work item list/Compansetion report/Compensation Report  till june.xlsx
+++ b/Task Report/Work item list/Compansetion report/Compensation Report  till june.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shahid Raza\Capitall\VSA project functionality\Task Report\Work item list\Compansetion report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5973CA-29C9-4F9E-AB08-C26686969879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949B3174-4EAB-4C78-A77D-8BBBFE459E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="7" xr2:uid="{2738ACE6-C0B7-4E71-8602-9B6BF8D304F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="8" xr2:uid="{2738ACE6-C0B7-4E71-8602-9B6BF8D304F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Dec" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="May" sheetId="8" r:id="rId6"/>
     <sheet name="June" sheetId="10" r:id="rId7"/>
     <sheet name="July" sheetId="11" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dec!$A$2:$D$36</definedName>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="26">
   <si>
     <t xml:space="preserve">Report For Compensation </t>
   </si>
@@ -100,6 +101,30 @@
   </si>
   <si>
     <t>Total Persent</t>
+  </si>
+  <si>
+    <t>aug</t>
+  </si>
+  <si>
+    <t>sep</t>
+  </si>
+  <si>
+    <t>oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nov </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 ya 22 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total mila </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total mila </t>
+  </si>
+  <si>
+    <t xml:space="preserve">end  hare to goes to client place </t>
   </si>
 </sst>
 </file>
@@ -163,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -179,6 +204,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2082,7 +2108,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" customWidth="1"/>
@@ -2443,6 +2469,17 @@
       <c r="B37">
         <f>COUNTIF(C2:C35, 80)</f>
         <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="7">
+        <v>45453</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40">
+        <v>7760</v>
       </c>
     </row>
   </sheetData>
@@ -3200,7 +3237,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E97BB21-49B6-4188-BB97-563CAE781A1A}">
-  <dimension ref="A1:D39"/>
+  <sheetPr>
+    <tabColor rgb="FF002060"/>
+  </sheetPr>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.90625" customWidth="1"/>
@@ -3622,10 +3662,72 @@
         <v>24</v>
       </c>
     </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41">
+        <v>3720</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC53F47-08AC-445B-B414-1B2A87543448}">
+  <dimension ref="A3:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>